--- a/research/traditional_assets/database/data/hong_kong/hong_kong_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_insurance_prop_cas.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.07585</v>
+        <v>-0.0541</v>
       </c>
       <c r="E2">
-        <v>0.1684</v>
+        <v>0.118</v>
       </c>
       <c r="G2">
-        <v>0.7124217118997912</v>
+        <v>0.217948717948718</v>
       </c>
       <c r="H2">
-        <v>0.7124217118997912</v>
+        <v>0.217948717948718</v>
       </c>
       <c r="I2">
-        <v>0.7590814196242172</v>
+        <v>0.1948717948717949</v>
       </c>
       <c r="J2">
-        <v>0.732781585110211</v>
+        <v>0.1905165851005982</v>
       </c>
       <c r="K2">
-        <v>80.5</v>
+        <v>59.9</v>
       </c>
       <c r="L2">
-        <v>0.8402922755741128</v>
+        <v>1.919871794871795</v>
       </c>
       <c r="M2">
-        <v>7.69</v>
+        <v>8.959499999999998</v>
       </c>
       <c r="N2">
-        <v>0.02258443465491924</v>
+        <v>0.03990868596881959</v>
       </c>
       <c r="O2">
-        <v>0.09552795031055901</v>
+        <v>0.1495742904841402</v>
       </c>
       <c r="P2">
-        <v>7.69</v>
+        <v>8.959499999999998</v>
       </c>
       <c r="Q2">
-        <v>0.02258443465491924</v>
+        <v>0.03990868596881959</v>
       </c>
       <c r="R2">
-        <v>0.09552795031055901</v>
+        <v>0.1495742904841402</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>296.8</v>
+        <v>88.5</v>
       </c>
       <c r="V2">
-        <v>0.8716593245227606</v>
+        <v>0.3942093541202673</v>
       </c>
       <c r="W2">
-        <v>0.283793018846883</v>
+        <v>0.05913129318854887</v>
       </c>
       <c r="X2">
-        <v>0.07586648751989911</v>
+        <v>0.1008319432076162</v>
       </c>
       <c r="Y2">
-        <v>0.2079265313269839</v>
+        <v>-0.04170065001906734</v>
       </c>
       <c r="Z2">
-        <v>0.1150060024009604</v>
+        <v>0.03215831787260359</v>
       </c>
       <c r="AA2">
-        <v>-0.05693762716743821</v>
+        <v>0.006126692903667967</v>
       </c>
       <c r="AB2">
-        <v>0.05510567852775364</v>
+        <v>0.08830114666939899</v>
       </c>
       <c r="AC2">
-        <v>-0.1120433056951919</v>
+        <v>-0.08217445376573103</v>
       </c>
       <c r="AD2">
-        <v>119.4</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>119.4</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="AG2">
-        <v>-177.4</v>
+        <v>-10.90000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.2596216568819309</v>
+        <v>0.2568685865607415</v>
       </c>
       <c r="AI2">
-        <v>0.0982635174059748</v>
+        <v>0.06877603474253301</v>
       </c>
       <c r="AJ2">
-        <v>-1.087676272225629</v>
+        <v>-0.05102996254681651</v>
       </c>
       <c r="AK2">
-        <v>-0.1931830556463029</v>
+        <v>-0.01048278515099058</v>
       </c>
       <c r="AL2">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="AM2">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="AN2">
-        <v>1.579365079365079</v>
+        <v>12.416</v>
       </c>
       <c r="AO2">
-        <v>33.05454545454545</v>
+        <v>3.268817204301075</v>
       </c>
       <c r="AP2">
-        <v>-2.346560846560847</v>
+        <v>-1.744000000000001</v>
       </c>
       <c r="AQ2">
-        <v>33.05454545454545</v>
+        <v>3.268817204301075</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0659</v>
+        <v>-0.0541</v>
       </c>
       <c r="E3">
-        <v>0.0888</v>
+        <v>0.118</v>
       </c>
       <c r="G3">
-        <v>2.307392996108949</v>
+        <v>0.217948717948718</v>
       </c>
       <c r="H3">
-        <v>2.307392996108949</v>
+        <v>0.217948717948718</v>
       </c>
       <c r="I3">
-        <v>2.470817120622568</v>
+        <v>0.1948717948717949</v>
       </c>
       <c r="J3">
-        <v>2.300133222998868</v>
+        <v>0.1905165851005982</v>
       </c>
       <c r="K3">
-        <v>61.8</v>
+        <v>59.9</v>
       </c>
       <c r="L3">
-        <v>2.404669260700389</v>
+        <v>1.919871794871795</v>
       </c>
       <c r="M3">
-        <v>7.69</v>
+        <v>8.959499999999998</v>
       </c>
       <c r="N3">
-        <v>0.02522965879265092</v>
+        <v>0.03990868596881959</v>
       </c>
       <c r="O3">
-        <v>0.1244336569579288</v>
+        <v>0.1495742904841402</v>
       </c>
       <c r="P3">
-        <v>7.69</v>
+        <v>8.959499999999998</v>
       </c>
       <c r="Q3">
-        <v>0.02522965879265092</v>
+        <v>0.03990868596881959</v>
       </c>
       <c r="R3">
-        <v>0.1244336569579288</v>
+        <v>0.1495742904841402</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,204 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>118.5</v>
+        <v>88.5</v>
       </c>
       <c r="V3">
-        <v>0.3887795275590551</v>
+        <v>0.3942093541202673</v>
       </c>
       <c r="W3">
-        <v>0.06891937102709936</v>
+        <v>0.05913129318854887</v>
       </c>
       <c r="X3">
-        <v>0.06053636369704002</v>
+        <v>0.1008319432076162</v>
       </c>
       <c r="Y3">
-        <v>0.008383007330059339</v>
+        <v>-0.04170065001906734</v>
       </c>
       <c r="Z3">
-        <v>0.02907239819004524</v>
+        <v>0.03215831787260359</v>
       </c>
       <c r="AA3">
-        <v>0.0668703889491752</v>
+        <v>0.006126692903667967</v>
       </c>
       <c r="AB3">
-        <v>0.05399252881141873</v>
+        <v>0.08830114666939899</v>
       </c>
       <c r="AC3">
-        <v>0.01287786013775647</v>
+        <v>-0.08217445376573103</v>
       </c>
       <c r="AD3">
-        <v>75.7</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>75.7</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="AG3">
-        <v>-42.8</v>
+        <v>-10.90000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.1989487516425756</v>
+        <v>0.2568685865607415</v>
       </c>
       <c r="AI3">
-        <v>0.06953246991825113</v>
+        <v>0.06877603474253301</v>
       </c>
       <c r="AJ3">
-        <v>-0.1633587786259542</v>
+        <v>-0.05102996254681651</v>
       </c>
       <c r="AK3">
-        <v>-0.04411461554318696</v>
+        <v>-0.01048278515099058</v>
       </c>
       <c r="AL3">
-        <v>1.17</v>
+        <v>1.86</v>
       </c>
       <c r="AM3">
-        <v>1.17</v>
+        <v>1.86</v>
       </c>
       <c r="AN3">
-        <v>1.188383045525903</v>
+        <v>12.416</v>
       </c>
       <c r="AO3">
-        <v>54.27350427350428</v>
+        <v>3.268817204301075</v>
       </c>
       <c r="AP3">
-        <v>-0.6718995290423861</v>
+        <v>-1.744000000000001</v>
       </c>
       <c r="AQ3">
-        <v>54.27350427350428</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Hong Kong</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Target Insurance (Holdings) Limited (SEHK:6161)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Insurance (Prop/Cas.)</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>0.0858</v>
-      </c>
-      <c r="E4">
-        <v>0.248</v>
-      </c>
-      <c r="G4">
-        <v>0.1276747503566334</v>
-      </c>
-      <c r="H4">
-        <v>0.1276747503566334</v>
-      </c>
-      <c r="I4">
-        <v>0.1315263908701855</v>
-      </c>
-      <c r="J4">
-        <v>0.1314982568828336</v>
-      </c>
-      <c r="K4">
-        <v>18.7</v>
-      </c>
-      <c r="L4">
-        <v>0.2667617689015692</v>
-      </c>
-      <c r="M4">
-        <v>-0</v>
-      </c>
-      <c r="N4">
-        <v>-0</v>
-      </c>
-      <c r="O4">
-        <v>-0</v>
-      </c>
-      <c r="P4">
-        <v>-0</v>
-      </c>
-      <c r="Q4">
-        <v>-0</v>
-      </c>
-      <c r="R4">
-        <v>-0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>178.3</v>
-      </c>
-      <c r="V4">
-        <v>4.994397759103641</v>
-      </c>
-      <c r="W4">
-        <v>0.4986666666666666</v>
-      </c>
-      <c r="X4">
-        <v>0.09119661134275821</v>
-      </c>
-      <c r="Y4">
-        <v>0.4074700553239085</v>
-      </c>
-      <c r="Z4">
-        <v>-1.374509803921569</v>
-      </c>
-      <c r="AA4">
-        <v>-0.1807456432840516</v>
-      </c>
-      <c r="AB4">
-        <v>0.05621882824408855</v>
-      </c>
-      <c r="AC4">
-        <v>-0.2369644715281402</v>
-      </c>
-      <c r="AD4">
-        <v>43.7</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>43.7</v>
-      </c>
-      <c r="AG4">
-        <v>-134.6</v>
-      </c>
-      <c r="AH4">
-        <v>0.5503778337531486</v>
-      </c>
-      <c r="AI4">
-        <v>0.3457278481012658</v>
-      </c>
-      <c r="AJ4">
-        <v>1.360970677451972</v>
-      </c>
-      <c r="AK4">
-        <v>2.593448940269749</v>
-      </c>
-      <c r="AL4">
-        <v>1.03</v>
-      </c>
-      <c r="AM4">
-        <v>1.03</v>
-      </c>
-      <c r="AN4">
-        <v>3.672268907563025</v>
-      </c>
-      <c r="AO4">
-        <v>8.951456310679612</v>
-      </c>
-      <c r="AP4">
-        <v>-11.3109243697479</v>
-      </c>
-      <c r="AQ4">
-        <v>8.951456310679612</v>
+        <v>3.268817204301075</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/hong_kong/hong_kong_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_insurance_prop_cas.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0541</v>
+        <v>-0.303</v>
       </c>
       <c r="E2">
-        <v>0.118</v>
+        <v>-0.1</v>
       </c>
       <c r="G2">
-        <v>0.217948717948718</v>
+        <v>0.1706896551724138</v>
       </c>
       <c r="H2">
-        <v>0.217948717948718</v>
+        <v>0.1706896551724138</v>
       </c>
       <c r="I2">
-        <v>0.1948717948717949</v>
+        <v>0.07965517241379311</v>
       </c>
       <c r="J2">
-        <v>0.1905165851005982</v>
+        <v>0.07588495079606368</v>
       </c>
       <c r="K2">
-        <v>59.9</v>
+        <v>41.1</v>
       </c>
       <c r="L2">
-        <v>1.919871794871795</v>
+        <v>1.417241379310345</v>
       </c>
       <c r="M2">
-        <v>8.959499999999998</v>
+        <v>9.15</v>
       </c>
       <c r="N2">
-        <v>0.03990868596881959</v>
+        <v>0.04112359550561798</v>
       </c>
       <c r="O2">
-        <v>0.1495742904841402</v>
+        <v>0.2226277372262774</v>
       </c>
       <c r="P2">
-        <v>8.959499999999998</v>
+        <v>9.15</v>
       </c>
       <c r="Q2">
-        <v>0.03990868596881959</v>
+        <v>0.04112359550561798</v>
       </c>
       <c r="R2">
-        <v>0.1495742904841402</v>
+        <v>0.2226277372262774</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>88.5</v>
+        <v>92.5</v>
       </c>
       <c r="V2">
-        <v>0.3942093541202673</v>
+        <v>0.4157303370786517</v>
       </c>
       <c r="W2">
-        <v>0.05913129318854887</v>
+        <v>0.03911677928999714</v>
       </c>
       <c r="X2">
-        <v>0.1008319432076162</v>
+        <v>0.08891576758075745</v>
       </c>
       <c r="Y2">
-        <v>-0.04170065001906734</v>
+        <v>-0.04979898829076031</v>
       </c>
       <c r="Z2">
-        <v>0.03215831787260359</v>
+        <v>0.02788997884208502</v>
       </c>
       <c r="AA2">
-        <v>0.006126692903667967</v>
+        <v>0.002116429672134879</v>
       </c>
       <c r="AB2">
-        <v>0.08830114666939899</v>
+        <v>0.07442577728836457</v>
       </c>
       <c r="AC2">
-        <v>-0.08217445376573103</v>
+        <v>-0.07230934761622969</v>
       </c>
       <c r="AD2">
-        <v>77.59999999999999</v>
+        <v>102.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>77.59999999999999</v>
+        <v>102.8</v>
       </c>
       <c r="AG2">
-        <v>-10.90000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="AH2">
-        <v>0.2568685865607415</v>
+        <v>0.3160159852443898</v>
       </c>
       <c r="AI2">
-        <v>0.06877603474253301</v>
+        <v>0.09017543859649123</v>
       </c>
       <c r="AJ2">
-        <v>-0.05102996254681651</v>
+        <v>0.04424398625429552</v>
       </c>
       <c r="AK2">
-        <v>-0.01048278515099058</v>
+        <v>0.009832935560859186</v>
       </c>
       <c r="AL2">
-        <v>1.86</v>
+        <v>3.78</v>
       </c>
       <c r="AM2">
-        <v>1.86</v>
+        <v>3.78</v>
       </c>
       <c r="AN2">
-        <v>12.416</v>
+        <v>40.79365079365079</v>
       </c>
       <c r="AO2">
-        <v>3.268817204301075</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="AP2">
-        <v>-1.744000000000001</v>
+        <v>4.087301587301586</v>
       </c>
       <c r="AQ2">
-        <v>3.268817204301075</v>
+        <v>0.6111111111111112</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0541</v>
+        <v>-0.303</v>
       </c>
       <c r="E3">
-        <v>0.118</v>
+        <v>-0.1</v>
       </c>
       <c r="G3">
-        <v>0.217948717948718</v>
+        <v>0.1706896551724138</v>
       </c>
       <c r="H3">
-        <v>0.217948717948718</v>
+        <v>0.1706896551724138</v>
       </c>
       <c r="I3">
-        <v>0.1948717948717949</v>
+        <v>0.07965517241379311</v>
       </c>
       <c r="J3">
-        <v>0.1905165851005982</v>
+        <v>0.07588495079606368</v>
       </c>
       <c r="K3">
-        <v>59.9</v>
+        <v>41.1</v>
       </c>
       <c r="L3">
-        <v>1.919871794871795</v>
+        <v>1.417241379310345</v>
       </c>
       <c r="M3">
-        <v>8.959499999999998</v>
+        <v>9.15</v>
       </c>
       <c r="N3">
-        <v>0.03990868596881959</v>
+        <v>0.04112359550561798</v>
       </c>
       <c r="O3">
-        <v>0.1495742904841402</v>
+        <v>0.2226277372262774</v>
       </c>
       <c r="P3">
-        <v>8.959499999999998</v>
+        <v>9.15</v>
       </c>
       <c r="Q3">
-        <v>0.03990868596881959</v>
+        <v>0.04112359550561798</v>
       </c>
       <c r="R3">
-        <v>0.1495742904841402</v>
+        <v>0.2226277372262774</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>88.5</v>
+        <v>92.5</v>
       </c>
       <c r="V3">
-        <v>0.3942093541202673</v>
+        <v>0.4157303370786517</v>
       </c>
       <c r="W3">
-        <v>0.05913129318854887</v>
+        <v>0.03911677928999714</v>
       </c>
       <c r="X3">
-        <v>0.1008319432076162</v>
+        <v>0.08891576758075745</v>
       </c>
       <c r="Y3">
-        <v>-0.04170065001906734</v>
+        <v>-0.04979898829076031</v>
       </c>
       <c r="Z3">
-        <v>0.03215831787260359</v>
+        <v>0.02788997884208502</v>
       </c>
       <c r="AA3">
-        <v>0.006126692903667967</v>
+        <v>0.002116429672134879</v>
       </c>
       <c r="AB3">
-        <v>0.08830114666939899</v>
+        <v>0.07442577728836457</v>
       </c>
       <c r="AC3">
-        <v>-0.08217445376573103</v>
+        <v>-0.07230934761622969</v>
       </c>
       <c r="AD3">
-        <v>77.59999999999999</v>
+        <v>102.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>77.59999999999999</v>
+        <v>102.8</v>
       </c>
       <c r="AG3">
-        <v>-10.90000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="AH3">
-        <v>0.2568685865607415</v>
+        <v>0.3160159852443898</v>
       </c>
       <c r="AI3">
-        <v>0.06877603474253301</v>
+        <v>0.09017543859649123</v>
       </c>
       <c r="AJ3">
-        <v>-0.05102996254681651</v>
+        <v>0.04424398625429552</v>
       </c>
       <c r="AK3">
-        <v>-0.01048278515099058</v>
+        <v>0.009832935560859186</v>
       </c>
       <c r="AL3">
-        <v>1.86</v>
+        <v>3.78</v>
       </c>
       <c r="AM3">
-        <v>1.86</v>
+        <v>3.78</v>
       </c>
       <c r="AN3">
-        <v>12.416</v>
+        <v>40.79365079365079</v>
       </c>
       <c r="AO3">
-        <v>3.268817204301075</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="AP3">
-        <v>-1.744000000000001</v>
+        <v>4.087301587301586</v>
       </c>
       <c r="AQ3">
-        <v>3.268817204301075</v>
+        <v>0.6111111111111112</v>
       </c>
     </row>
   </sheetData>
